--- a/Raw Data/DATA.xlsx
+++ b/Raw Data/DATA.xlsx
@@ -23,22 +23,22 @@
     <t>Total Waste</t>
   </si>
   <si>
-    <t>MRF</t>
+    <t xml:space="preserve">Dengue </t>
   </si>
   <si>
-    <t xml:space="preserve">Dengue </t>
+    <t>MRF</t>
   </si>
   <si>
     <t>Composting</t>
   </si>
   <si>
-    <t>Collection Segregation</t>
+    <t>Gastroenteritis</t>
+  </si>
+  <si>
+    <t>Reported Collection Segregation</t>
   </si>
   <si>
     <t>RCA</t>
-  </si>
-  <si>
-    <t>Gastroenteritis</t>
   </si>
   <si>
     <t>Private Hauler</t>
@@ -47,40 +47,40 @@
     <t>Dumpsite</t>
   </si>
   <si>
+    <t>Bronchial Asthma</t>
+  </si>
+  <si>
     <t>SLF</t>
   </si>
   <si>
-    <t>Bronchial Asthma</t>
+    <t>Special Waste Storage</t>
   </si>
   <si>
     <t>Dermatitis</t>
   </si>
   <si>
-    <t>Special Waste Storage</t>
+    <t>Biodegradable</t>
   </si>
   <si>
     <t>Chronic Obstructive Pulmonary Disease</t>
   </si>
   <si>
-    <t>Biodegradable</t>
+    <t>Recyclable</t>
   </si>
   <si>
     <t xml:space="preserve">Leptospirosis </t>
   </si>
   <si>
-    <t>Recyclable</t>
+    <t>Residual</t>
+  </si>
+  <si>
+    <t>Special</t>
   </si>
   <si>
     <t>Pulmonary Hypertension</t>
   </si>
   <si>
-    <t>Residual</t>
-  </si>
-  <si>
     <t>Helminth Infection</t>
-  </si>
-  <si>
-    <t>Special</t>
   </si>
   <si>
     <t>Malnutrition</t>
@@ -146,13 +146,13 @@
     <t>Carcar</t>
   </si>
   <si>
+    <t>NONE</t>
+  </si>
+  <si>
     <t>Carmen</t>
   </si>
   <si>
     <t>Catmon</t>
-  </si>
-  <si>
-    <t>NONE</t>
   </si>
   <si>
     <t>Compostela</t>
@@ -323,20 +323,20 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -599,16 +599,16 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>9</v>
@@ -617,22 +617,22 @@
         <v>10</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="P1" s="4"/>
       <c r="Q1" s="4"/>
@@ -641,2202 +641,2202 @@
       <c r="T1" s="4"/>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="7">
         <v>4874.14</v>
       </c>
-      <c r="C2" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D2" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E2" s="10" t="s">
+      <c r="C2" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" s="10" t="b">
+      <c r="F2" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H2" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="10" t="b">
+      <c r="H2" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="J2" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K2" s="8">
+      <c r="J2" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" s="7">
         <v>1959.05</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="7">
         <v>961.12</v>
       </c>
-      <c r="M2" s="8">
+      <c r="M2" s="7">
         <v>1861.18</v>
       </c>
-      <c r="N2" s="8">
+      <c r="N2" s="7">
         <v>92.79</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="7">
         <v>1939.71</v>
       </c>
-      <c r="C3" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D3" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E3" s="10" t="s">
+      <c r="C3" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="H3" s="10" t="b">
+      <c r="F3" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I3" s="10" t="b">
+      <c r="I3" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="J3" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K3" s="8">
+      <c r="J3" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" s="7">
         <v>818.5</v>
       </c>
-      <c r="L3" s="8">
+      <c r="L3" s="7">
         <v>390.31</v>
       </c>
-      <c r="M3" s="8">
+      <c r="M3" s="7">
         <v>669.3</v>
       </c>
-      <c r="N3" s="8">
+      <c r="N3" s="7">
         <v>61.6</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="7">
         <v>7257.9</v>
       </c>
-      <c r="C4" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D4" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" s="10" t="s">
+      <c r="C4" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="10" t="b">
+      <c r="F4" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="G4" s="10" t="b">
+      <c r="G4" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H4" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="10" t="b">
+      <c r="H4" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="J4" s="10" t="b">
+      <c r="J4" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K4" s="7">
         <v>3193.48</v>
       </c>
-      <c r="L4" s="8">
+      <c r="L4" s="7">
         <v>1669.32</v>
       </c>
-      <c r="M4" s="8">
+      <c r="M4" s="7">
         <v>2322.53</v>
       </c>
-      <c r="N4" s="8">
+      <c r="N4" s="7">
         <v>72.58</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B5" s="11">
         <v>10258.97</v>
       </c>
-      <c r="C5" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D5" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="10" t="s">
+      <c r="C5" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="10" t="b">
+      <c r="F5" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="G5" s="10" t="b">
+      <c r="G5" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H5" s="10" t="b">
+      <c r="H5" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I5" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J5" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" s="8">
+      <c r="I5" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" s="7">
         <v>4513.95</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="7">
         <v>2359.56</v>
       </c>
-      <c r="M5" s="8">
+      <c r="M5" s="7">
         <v>3282.87</v>
       </c>
-      <c r="N5" s="8">
+      <c r="N5" s="7">
         <v>102.59</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="7">
         <v>19648.01</v>
       </c>
-      <c r="C6" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D6" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="10" t="s">
+      <c r="C6" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="10" t="b">
+      <c r="F6" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H6" s="10" t="b">
+      <c r="H6" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I6" s="10" t="b">
+      <c r="I6" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="J6" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="8">
+      <c r="J6" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="7">
         <v>9002.29</v>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="7">
         <v>2565.18</v>
       </c>
-      <c r="M6" s="8">
+      <c r="M6" s="7">
         <v>7948.77</v>
       </c>
-      <c r="N6" s="8">
+      <c r="N6" s="7">
         <v>131.78</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="7">
         <v>9277.81</v>
       </c>
-      <c r="C7" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D7" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="10" t="s">
+      <c r="C7" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="10" t="b">
+      <c r="F7" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="G7" s="10" t="b">
+      <c r="G7" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H7" s="10" t="b">
+      <c r="H7" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I7" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="8">
+      <c r="I7" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="7">
         <v>5048.62</v>
       </c>
-      <c r="L7" s="8">
+      <c r="L7" s="7">
         <v>315.05</v>
       </c>
-      <c r="M7" s="8">
+      <c r="M7" s="7">
         <v>3914.15</v>
       </c>
-      <c r="N7" s="8">
+      <c r="N7" s="7">
         <v>0.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="7">
         <v>13137.77</v>
       </c>
-      <c r="C8" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D8" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="10" t="s">
+      <c r="C8" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="10" t="b">
+      <c r="F8" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H8" s="10" t="b">
+      <c r="H8" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I8" s="10" t="b">
+      <c r="I8" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="J8" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" s="8">
+      <c r="J8" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" s="7">
         <v>5780.61</v>
       </c>
-      <c r="L8" s="8">
+      <c r="L8" s="7">
         <v>3021.69</v>
       </c>
-      <c r="M8" s="8">
+      <c r="M8" s="7">
         <v>4204.09</v>
       </c>
-      <c r="N8" s="8">
+      <c r="N8" s="7">
         <v>131.38</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="7">
         <v>11473.92</v>
       </c>
-      <c r="C9" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D9" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="10" t="s">
+      <c r="C9" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="10" t="b">
+      <c r="F9" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="G9" s="10" t="b">
+      <c r="G9" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H9" s="10" t="b">
+      <c r="H9" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I9" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J9" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" s="8">
+      <c r="I9" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" s="7">
         <v>5206.86</v>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="7">
         <v>2314.29</v>
       </c>
-      <c r="M9" s="8">
+      <c r="M9" s="7">
         <v>3712.96</v>
       </c>
-      <c r="N9" s="8">
+      <c r="N9" s="7">
         <v>239.81</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="7">
         <v>34727.53</v>
       </c>
-      <c r="C10" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D10" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="10" t="s">
+      <c r="C10" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D10" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" s="10" t="b">
+      <c r="F10" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H10" s="10" t="b">
+      <c r="H10" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I10" s="10" t="b">
+      <c r="I10" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="J10" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" s="8">
+      <c r="J10" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" s="7">
         <v>24145.78</v>
       </c>
-      <c r="L10" s="8">
+      <c r="L10" s="7">
         <v>6051.91</v>
       </c>
-      <c r="M10" s="8">
+      <c r="M10" s="7">
         <v>3727.87</v>
       </c>
-      <c r="N10" s="8">
+      <c r="N10" s="7">
         <v>801.98</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="7">
         <v>8391.25</v>
       </c>
-      <c r="C11" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D11" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="10" t="s">
+      <c r="C11" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D11" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" s="10" t="b">
+      <c r="F11" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H11" s="10" t="b">
+      <c r="H11" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I11" s="10" t="b">
+      <c r="I11" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="J11" s="10" t="b">
+      <c r="J11" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="K11" s="8">
+      <c r="K11" s="7">
         <v>6144.19</v>
       </c>
-      <c r="L11" s="8">
+      <c r="L11" s="7">
         <v>661.45</v>
       </c>
-      <c r="M11" s="8">
+      <c r="M11" s="7">
         <v>1369.91</v>
       </c>
-      <c r="N11" s="8">
+      <c r="N11" s="7">
         <v>215.7</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="7">
         <v>18239.2</v>
       </c>
-      <c r="C12" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D12" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="10" t="s">
+      <c r="C12" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="10" t="b">
+      <c r="F12" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H12" s="10" t="b">
+      <c r="H12" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I12" s="10" t="b">
+      <c r="I12" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="J12" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K12" s="8">
+      <c r="J12" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" s="7">
         <v>8025.25</v>
       </c>
-      <c r="L12" s="8">
+      <c r="L12" s="7">
         <v>4195.02</v>
       </c>
-      <c r="M12" s="8">
+      <c r="M12" s="7">
         <v>5836.54</v>
       </c>
-      <c r="N12" s="8">
+      <c r="N12" s="7">
         <v>182.39</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="7">
         <v>2707.99</v>
       </c>
-      <c r="C13" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D13" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="10" t="s">
+      <c r="C13" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" s="10" t="b">
+      <c r="F13" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H13" s="10" t="b">
+      <c r="H13" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I13" s="10" t="b">
+      <c r="I13" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="J13" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K13" s="8">
+      <c r="J13" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" s="7">
         <v>1191.51</v>
       </c>
-      <c r="L13" s="8">
+      <c r="L13" s="7">
         <v>622.84</v>
       </c>
-      <c r="M13" s="8">
+      <c r="M13" s="7">
         <v>866.55</v>
       </c>
-      <c r="N13" s="8">
+      <c r="N13" s="7">
         <v>27.08</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="7">
         <v>11256.28</v>
       </c>
-      <c r="C14" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D14" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="10" t="s">
+      <c r="C14" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D14" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14" s="10" t="b">
+      <c r="F14" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H14" s="10" t="b">
+      <c r="H14" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I14" s="10" t="b">
+      <c r="I14" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="J14" s="10" t="b">
+      <c r="J14" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="7">
         <v>4952.77</v>
       </c>
-      <c r="L14" s="8">
+      <c r="L14" s="7">
         <v>2588.95</v>
       </c>
-      <c r="M14" s="8">
+      <c r="M14" s="7">
         <v>3602.01</v>
       </c>
-      <c r="N14" s="8">
+      <c r="N14" s="7">
         <v>112.56</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="7">
         <v>32034.49</v>
       </c>
-      <c r="C15" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D15" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="10" t="s">
+      <c r="C15" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D15" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" s="7">
+        <v>12761.52</v>
+      </c>
+      <c r="L15" s="7">
+        <v>7831.27</v>
+      </c>
+      <c r="M15" s="7">
+        <v>10957.53</v>
+      </c>
+      <c r="N15" s="7">
+        <v>484.17</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="7">
+        <v>19077.6</v>
+      </c>
+      <c r="C16" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D16" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" s="7">
+        <v>8394.14</v>
+      </c>
+      <c r="L16" s="7">
+        <v>4387.85</v>
+      </c>
+      <c r="M16" s="7">
+        <v>6104.83</v>
+      </c>
+      <c r="N16" s="7">
+        <v>190.77</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="10" t="b">
+      <c r="B17" s="7">
+        <v>6214.65</v>
+      </c>
+      <c r="C17" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D17" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="G15" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" s="10" t="b">
+      <c r="H17" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I15" s="10" t="b">
+      <c r="I17" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="J15" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K15" s="8">
-        <v>12761.52</v>
-      </c>
-      <c r="L15" s="8">
-        <v>7831.27</v>
-      </c>
-      <c r="M15" s="8">
-        <v>10957.53</v>
-      </c>
-      <c r="N15" s="8">
-        <v>484.17</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="s">
+      <c r="J17" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" s="7">
+        <v>2969.37</v>
+      </c>
+      <c r="L17" s="7">
+        <v>2383.94</v>
+      </c>
+      <c r="M17" s="7">
+        <v>581.69</v>
+      </c>
+      <c r="N17" s="7">
+        <v>279.66</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="7">
+        <v>12346.5</v>
+      </c>
+      <c r="C18" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D18" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" s="7">
+        <v>9116.93</v>
+      </c>
+      <c r="L18" s="7">
+        <v>1330.9</v>
+      </c>
+      <c r="M18" s="7">
+        <v>1798.49</v>
+      </c>
+      <c r="N18" s="7">
+        <v>100.18</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="7">
+        <v>78791.72</v>
+      </c>
+      <c r="C19" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D19" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" s="7">
+        <v>22598.37</v>
+      </c>
+      <c r="L19" s="7">
+        <v>23328.02</v>
+      </c>
+      <c r="M19" s="7">
+        <v>32306.15</v>
+      </c>
+      <c r="N19" s="7">
+        <v>559.17</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="7">
+        <v>17507.26</v>
+      </c>
+      <c r="C20" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D20" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" s="7">
+        <v>6978.11</v>
+      </c>
+      <c r="L20" s="7">
+        <v>3751.9</v>
+      </c>
+      <c r="M20" s="7">
+        <v>6756.26</v>
+      </c>
+      <c r="N20" s="7">
+        <v>20.98</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="7">
+        <v>27563.48</v>
+      </c>
+      <c r="C21" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D21" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" s="7">
+        <v>15022.09</v>
+      </c>
+      <c r="L21" s="7">
+        <v>7224.39</v>
+      </c>
+      <c r="M21" s="7">
+        <v>4801.56</v>
+      </c>
+      <c r="N21" s="7">
+        <v>515.43</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="7">
+        <v>30084.95</v>
+      </c>
+      <c r="C22" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D22" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" s="7">
+        <v>16904.48</v>
+      </c>
+      <c r="L22" s="7">
+        <v>7644.7</v>
+      </c>
+      <c r="M22" s="7">
+        <v>4294.15</v>
+      </c>
+      <c r="N22" s="7">
+        <v>1241.62</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="7">
+        <v>40531.16</v>
+      </c>
+      <c r="C23" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D23" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" s="7">
+        <v>19715.21</v>
+      </c>
+      <c r="L23" s="7">
+        <v>8287.37</v>
+      </c>
+      <c r="M23" s="7">
+        <v>11401.57</v>
+      </c>
+      <c r="N23" s="7">
+        <v>1127.02</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="7">
+        <v>18787.09</v>
+      </c>
+      <c r="C24" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D24" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="8">
-        <v>19077.6</v>
-      </c>
-      <c r="C16" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D16" s="10" t="b">
+      <c r="F24" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="F16" s="10" t="b">
+      <c r="G24" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="G16" s="10" t="b">
+      <c r="H24" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H16" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I16" s="10" t="b">
+      <c r="J24" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="J16" s="10" t="b">
+      <c r="K24" s="7">
+        <v>8266.32</v>
+      </c>
+      <c r="L24" s="7">
+        <v>4321.03</v>
+      </c>
+      <c r="M24" s="7">
+        <v>6011.87</v>
+      </c>
+      <c r="N24" s="7">
+        <v>187.87</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="7">
+        <v>5290.37</v>
+      </c>
+      <c r="C25" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D25" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F25" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G25" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="K16" s="8">
-        <v>8394.14</v>
-      </c>
-      <c r="L16" s="8">
-        <v>4387.85</v>
-      </c>
-      <c r="M16" s="8">
-        <v>6104.83</v>
-      </c>
-      <c r="N16" s="8">
-        <v>190.77</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="8">
-        <v>6214.65</v>
-      </c>
-      <c r="C17" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D17" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="10" t="s">
+      <c r="H25" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" s="7">
+        <v>2327.76</v>
+      </c>
+      <c r="L25" s="7">
+        <v>1216.79</v>
+      </c>
+      <c r="M25" s="7">
+        <v>1692.92</v>
+      </c>
+      <c r="N25" s="7">
+        <v>52.9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26" s="7">
+        <v>41492.22</v>
+      </c>
+      <c r="C26" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D26" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="10" t="b">
+      <c r="F26" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G26" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H17" s="10" t="b">
+      <c r="H26" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I17" s="10" t="b">
+      <c r="I26" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J26" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K26" s="7">
+        <v>18256.57</v>
+      </c>
+      <c r="L26" s="7">
+        <v>9543.21</v>
+      </c>
+      <c r="M26" s="7">
+        <v>13277.51</v>
+      </c>
+      <c r="N26" s="7">
+        <v>414.93</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="7">
+        <v>10096.7</v>
+      </c>
+      <c r="C27" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D27" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="J17" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K17" s="8">
-        <v>2969.37</v>
-      </c>
-      <c r="L17" s="8">
-        <v>2383.94</v>
-      </c>
-      <c r="M17" s="8">
-        <v>581.69</v>
-      </c>
-      <c r="N17" s="8">
-        <v>279.66</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" s="8">
-        <v>12346.5</v>
-      </c>
-      <c r="C18" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D18" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="10" t="s">
+      <c r="H27" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K27" s="7">
+        <v>4442.55</v>
+      </c>
+      <c r="L27" s="7">
+        <v>2322.24</v>
+      </c>
+      <c r="M27" s="7">
+        <v>3230.94</v>
+      </c>
+      <c r="N27" s="7">
+        <v>100.97</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" s="7">
+        <v>6459.87</v>
+      </c>
+      <c r="C28" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D28" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" s="10" t="b">
+      <c r="F28" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H18" s="10" t="b">
+      <c r="H28" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I18" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K18" s="8">
-        <v>9116.93</v>
-      </c>
-      <c r="L18" s="8">
-        <v>1330.9</v>
-      </c>
-      <c r="M18" s="8">
-        <v>1798.49</v>
-      </c>
-      <c r="N18" s="8">
-        <v>100.18</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19" s="8">
-        <v>78791.72</v>
-      </c>
-      <c r="C19" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D19" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" s="10" t="s">
+      <c r="I28" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J28" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K28" s="7">
+        <v>2842.35</v>
+      </c>
+      <c r="L28" s="7">
+        <v>1485.77</v>
+      </c>
+      <c r="M28" s="7">
+        <v>2067.16</v>
+      </c>
+      <c r="N28" s="7">
+        <v>64.6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="7">
+        <v>34675.14</v>
+      </c>
+      <c r="C29" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D29" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F29" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I29" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" s="7">
+        <v>16054.58</v>
+      </c>
+      <c r="L29" s="7">
+        <v>10173.69</v>
+      </c>
+      <c r="M29" s="7">
+        <v>7989.16</v>
+      </c>
+      <c r="N29" s="7">
+        <v>457.72</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="7">
+        <v>46013.98</v>
+      </c>
+      <c r="C30" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D30" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F30" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K30" s="7">
+        <v>20246.15</v>
+      </c>
+      <c r="L30" s="7">
+        <v>10583.21</v>
+      </c>
+      <c r="M30" s="7">
+        <v>14724.47</v>
+      </c>
+      <c r="N30" s="7">
+        <v>460.14</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="7">
+        <v>9863.42</v>
+      </c>
+      <c r="C31" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D31" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F19" s="10" t="b">
+      <c r="F31" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="G19" s="10" t="b">
+      <c r="H31" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H19" s="10" t="b">
+      <c r="I31" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I19" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K19" s="8">
-        <v>22598.37</v>
-      </c>
-      <c r="L19" s="8">
-        <v>23328.02</v>
-      </c>
-      <c r="M19" s="8">
-        <v>32306.15</v>
-      </c>
-      <c r="N19" s="8">
-        <v>559.17</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B20" s="8">
-        <v>17507.26</v>
-      </c>
-      <c r="C20" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D20" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" s="10" t="s">
+      <c r="J31" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K31" s="7">
+        <v>2749.54</v>
+      </c>
+      <c r="L31" s="7">
+        <v>3674.5</v>
+      </c>
+      <c r="M31" s="7">
+        <v>3393.55</v>
+      </c>
+      <c r="N31" s="7">
+        <v>45.83</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="7">
+        <v>48139.58</v>
+      </c>
+      <c r="C32" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D32" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F20" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G20" s="10" t="b">
+      <c r="F32" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H20" s="10" t="b">
+      <c r="G32" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I20" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J20" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K20" s="8">
-        <v>6978.11</v>
-      </c>
-      <c r="L20" s="8">
-        <v>3751.9</v>
-      </c>
-      <c r="M20" s="8">
-        <v>6756.26</v>
-      </c>
-      <c r="N20" s="8">
-        <v>20.98</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B21" s="8">
-        <v>27563.48</v>
-      </c>
-      <c r="C21" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D21" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" s="10" t="s">
+      <c r="I32" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K32" s="7">
+        <v>23903.61</v>
+      </c>
+      <c r="L32" s="7">
+        <v>11178.78</v>
+      </c>
+      <c r="M32" s="7">
+        <v>12264.43</v>
+      </c>
+      <c r="N32" s="7">
+        <v>792.76</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" s="7">
+        <v>8715.35</v>
+      </c>
+      <c r="C33" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D33" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F33" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I33" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" s="7">
+        <v>3834.88</v>
+      </c>
+      <c r="L33" s="7">
+        <v>2004.59</v>
+      </c>
+      <c r="M33" s="7">
+        <v>2789.0</v>
+      </c>
+      <c r="N33" s="7">
+        <v>86.88</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" s="7">
+        <v>3742.79</v>
+      </c>
+      <c r="C34" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D34" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F21" s="10" t="b">
+      <c r="F34" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="G21" s="10" t="b">
+      <c r="H34" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H21" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I21" s="10" t="b">
+      <c r="I34" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="J21" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K21" s="8">
-        <v>15022.09</v>
-      </c>
-      <c r="L21" s="8">
-        <v>7224.39</v>
-      </c>
-      <c r="M21" s="8">
-        <v>4801.56</v>
-      </c>
-      <c r="N21" s="8">
-        <v>515.43</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B22" s="8">
-        <v>30084.95</v>
-      </c>
-      <c r="C22" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D22" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" s="10" t="s">
+      <c r="J34" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K34" s="7">
+        <v>1646.83</v>
+      </c>
+      <c r="L34" s="7">
+        <v>860.84</v>
+      </c>
+      <c r="M34" s="7">
+        <v>1197.69</v>
+      </c>
+      <c r="N34" s="7">
+        <v>37.42</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B35" s="7">
+        <v>19801.0</v>
+      </c>
+      <c r="C35" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D35" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="10" t="b">
+      <c r="F35" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="G22" s="10" t="b">
+      <c r="G35" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H22" s="10" t="b">
+      <c r="H35" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I22" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K22" s="8">
-        <v>16904.48</v>
-      </c>
-      <c r="L22" s="8">
-        <v>7644.7</v>
-      </c>
-      <c r="M22" s="8">
-        <v>4294.15</v>
-      </c>
-      <c r="N22" s="8">
-        <v>1241.62</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" s="8">
-        <v>40531.16</v>
-      </c>
-      <c r="C23" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D23" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" s="10" t="s">
+      <c r="I35" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J35" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K35" s="7">
+        <v>8712.44</v>
+      </c>
+      <c r="L35" s="7">
+        <v>4554.23</v>
+      </c>
+      <c r="M35" s="7">
+        <v>6336.32</v>
+      </c>
+      <c r="N35" s="7">
+        <v>198.01</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B36" s="7">
+        <v>4187.86</v>
+      </c>
+      <c r="C36" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D36" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F23" s="10" t="b">
+      <c r="F36" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="G23" s="10" t="b">
+      <c r="H36" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H23" s="10" t="b">
+      <c r="I36" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I23" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J23" s="10" t="b">
+      <c r="J36" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K36" s="7">
+        <v>2443.24</v>
+      </c>
+      <c r="L36" s="7">
+        <v>496.53</v>
+      </c>
+      <c r="M36" s="7">
+        <v>1219.85</v>
+      </c>
+      <c r="N36" s="7">
+        <v>28.23</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" s="7">
+        <v>2524.91</v>
+      </c>
+      <c r="C37" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D37" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F37" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="K23" s="8">
-        <v>19715.21</v>
-      </c>
-      <c r="L23" s="8">
-        <v>8287.37</v>
-      </c>
-      <c r="M23" s="8">
-        <v>11401.57</v>
-      </c>
-      <c r="N23" s="8">
-        <v>1127.02</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B24" s="8">
-        <v>18787.09</v>
-      </c>
-      <c r="C24" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D24" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="F24" s="10" t="b">
+      <c r="H37" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="G24" s="10" t="b">
+      <c r="I37" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H24" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I24" s="10" t="b">
+      <c r="J37" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K37" s="7">
+        <v>1110.96</v>
+      </c>
+      <c r="L37" s="7">
+        <v>580.73</v>
+      </c>
+      <c r="M37" s="7">
+        <v>807.97</v>
+      </c>
+      <c r="N37" s="7">
+        <v>25.25</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B38" s="7">
+        <v>4696.11</v>
+      </c>
+      <c r="C38" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D38" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F38" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H38" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="J24" s="10" t="b">
+      <c r="I38" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="K24" s="8">
-        <v>8266.32</v>
-      </c>
-      <c r="L24" s="8">
-        <v>4321.03</v>
-      </c>
-      <c r="M24" s="8">
-        <v>6011.87</v>
-      </c>
-      <c r="N24" s="8">
-        <v>187.87</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B25" s="8">
-        <v>5290.37</v>
-      </c>
-      <c r="C25" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D25" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="10" t="s">
+      <c r="J38" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K38" s="7">
+        <v>2194.53</v>
+      </c>
+      <c r="L38" s="7">
+        <v>1323.29</v>
+      </c>
+      <c r="M38" s="7">
+        <v>1167.8</v>
+      </c>
+      <c r="N38" s="7">
+        <v>10.49</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B39" s="7">
+        <v>21689.28</v>
+      </c>
+      <c r="C39" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D39" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E39" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F25" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G25" s="10" t="b">
+      <c r="F39" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H25" s="10" t="b">
+      <c r="H39" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I39" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I25" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J25" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K25" s="8">
-        <v>2327.76</v>
-      </c>
-      <c r="L25" s="8">
-        <v>1216.79</v>
-      </c>
-      <c r="M25" s="8">
-        <v>1692.92</v>
-      </c>
-      <c r="N25" s="8">
-        <v>52.9</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B26" s="8">
-        <v>41492.22</v>
-      </c>
-      <c r="C26" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D26" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="10" t="s">
+      <c r="J39" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K39" s="7">
+        <v>11277.07</v>
+      </c>
+      <c r="L39" s="7">
+        <v>3791.42</v>
+      </c>
+      <c r="M39" s="7">
+        <v>6427.99</v>
+      </c>
+      <c r="N39" s="7">
+        <v>192.79</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B40" s="7">
+        <v>20527.38</v>
+      </c>
+      <c r="C40" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D40" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F26" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G26" s="10" t="b">
+      <c r="F40" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H26" s="10" t="b">
+      <c r="H40" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I26" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J26" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K26" s="8">
-        <v>18256.57</v>
-      </c>
-      <c r="L26" s="8">
-        <v>9543.21</v>
-      </c>
-      <c r="M26" s="8">
-        <v>13277.51</v>
-      </c>
-      <c r="N26" s="8">
-        <v>414.93</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" s="8">
-        <v>10096.7</v>
-      </c>
-      <c r="C27" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D27" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" s="10" t="s">
+      <c r="I40" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K40" s="7">
+        <v>3650.8</v>
+      </c>
+      <c r="L40" s="7">
+        <v>5707.92</v>
+      </c>
+      <c r="M40" s="7">
+        <v>10576.26</v>
+      </c>
+      <c r="N40" s="7">
+        <v>592.41</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B41" s="7">
+        <v>8307.15</v>
+      </c>
+      <c r="C41" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D41" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F27" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G27" s="10" t="b">
+      <c r="F41" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H27" s="10" t="b">
+      <c r="H41" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I27" s="10" t="b">
+      <c r="I41" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J41" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K41" s="7">
+        <v>5244.19</v>
+      </c>
+      <c r="L41" s="7">
+        <v>677.21</v>
+      </c>
+      <c r="M41" s="7">
+        <v>2277.39</v>
+      </c>
+      <c r="N41" s="7">
+        <v>108.36</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B42" s="7">
+        <v>5793.88</v>
+      </c>
+      <c r="C42" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D42" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F42" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="J27" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K27" s="8">
-        <v>4442.55</v>
-      </c>
-      <c r="L27" s="8">
-        <v>2322.24</v>
-      </c>
-      <c r="M27" s="8">
-        <v>3230.94</v>
-      </c>
-      <c r="N27" s="8">
-        <v>100.97</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B28" s="8">
-        <v>6459.87</v>
-      </c>
-      <c r="C28" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D28" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E28" s="10" t="s">
+      <c r="H42" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K42" s="7">
+        <v>2491.37</v>
+      </c>
+      <c r="L42" s="7">
+        <v>2665.18</v>
+      </c>
+      <c r="M42" s="7">
+        <v>579.39</v>
+      </c>
+      <c r="N42" s="7">
+        <v>57.94</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B43" s="7">
+        <v>5508.14</v>
+      </c>
+      <c r="C43" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D43" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F43" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G43" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I43" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K43" s="7">
+        <v>2423.58</v>
+      </c>
+      <c r="L43" s="7">
+        <v>1266.87</v>
+      </c>
+      <c r="M43" s="7">
+        <v>1762.61</v>
+      </c>
+      <c r="N43" s="7">
+        <v>55.08</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B44" s="7">
+        <v>10208.23</v>
+      </c>
+      <c r="C44" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D44" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F44" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H44" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I44" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K44" s="7">
+        <v>4090.31</v>
+      </c>
+      <c r="L44" s="7">
+        <v>2064.78</v>
+      </c>
+      <c r="M44" s="7">
+        <v>3963.39</v>
+      </c>
+      <c r="N44" s="7">
+        <v>89.75</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B45" s="7">
+        <v>11181.33</v>
+      </c>
+      <c r="C45" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D45" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F28" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" s="10" t="b">
+      <c r="F45" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H28" s="10" t="b">
+      <c r="H45" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I28" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J28" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K28" s="8">
-        <v>2842.35</v>
-      </c>
-      <c r="L28" s="8">
-        <v>1485.77</v>
-      </c>
-      <c r="M28" s="8">
-        <v>2067.16</v>
-      </c>
-      <c r="N28" s="8">
-        <v>64.6</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="8">
-        <v>34675.14</v>
-      </c>
-      <c r="C29" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D29" s="10" t="b">
+      <c r="I45" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="E29" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="F29" s="10" t="b">
+      <c r="J45" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K45" s="7">
+        <v>7228.49</v>
+      </c>
+      <c r="L45" s="7">
+        <v>554.05</v>
+      </c>
+      <c r="M45" s="7">
+        <v>3322.33</v>
+      </c>
+      <c r="N45" s="7">
+        <v>76.46</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="B46" s="7">
+        <v>15914.36</v>
+      </c>
+      <c r="C46" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D46" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F46" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="G29" s="10" t="b">
+      <c r="G46" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H29" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I29" s="10" t="b">
+      <c r="H46" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I46" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="J29" s="10" t="b">
+      <c r="J46" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="K29" s="8">
-        <v>16054.58</v>
-      </c>
-      <c r="L29" s="8">
-        <v>10173.69</v>
-      </c>
-      <c r="M29" s="8">
-        <v>7989.16</v>
-      </c>
-      <c r="N29" s="8">
-        <v>457.72</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B30" s="8">
-        <v>46013.98</v>
-      </c>
-      <c r="C30" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D30" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="F30" s="10" t="b">
+      <c r="K46" s="7">
+        <v>8727.37</v>
+      </c>
+      <c r="L46" s="7">
+        <v>355.16</v>
+      </c>
+      <c r="M46" s="7">
+        <v>6523.94</v>
+      </c>
+      <c r="N46" s="7">
+        <v>307.88</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B47" s="7">
+        <v>4044.86</v>
+      </c>
+      <c r="C47" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D47" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F47" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="G30" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="H30" s="10" t="b">
+      <c r="H47" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I30" s="10" t="b">
+      <c r="I47" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="J30" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K30" s="8">
-        <v>20246.15</v>
-      </c>
-      <c r="L30" s="8">
-        <v>10583.21</v>
-      </c>
-      <c r="M30" s="8">
-        <v>14724.47</v>
-      </c>
-      <c r="N30" s="8">
-        <v>460.14</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" s="8">
-        <v>9863.42</v>
-      </c>
-      <c r="C31" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D31" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" s="10" t="s">
+      <c r="J47" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K47" s="7">
+        <v>3308.82</v>
+      </c>
+      <c r="L47" s="7">
+        <v>136.9</v>
+      </c>
+      <c r="M47" s="7">
+        <v>599.05</v>
+      </c>
+      <c r="N47" s="7">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B48" s="7">
+        <v>98897.61</v>
+      </c>
+      <c r="C48" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D48" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F48" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G48" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I48" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J48" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K48" s="7">
+        <v>43514.95</v>
+      </c>
+      <c r="L48" s="7">
+        <v>22746.45</v>
+      </c>
+      <c r="M48" s="7">
+        <v>31647.23</v>
+      </c>
+      <c r="N48" s="7">
+        <v>988.98</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B49" s="7">
+        <v>73107.65</v>
+      </c>
+      <c r="C49" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D49" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F49" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G49" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I49" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J49" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K49" s="7">
+        <v>32167.37</v>
+      </c>
+      <c r="L49" s="7">
+        <v>16814.76</v>
+      </c>
+      <c r="M49" s="7">
+        <v>23394.44</v>
+      </c>
+      <c r="N49" s="7">
+        <v>731.08</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B50" s="7">
+        <v>16316.21</v>
+      </c>
+      <c r="C50" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D50" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F50" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G50" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I50" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K50" s="7">
+        <v>8158.11</v>
+      </c>
+      <c r="L50" s="7">
+        <v>5710.67</v>
+      </c>
+      <c r="M50" s="7">
+        <v>1957.95</v>
+      </c>
+      <c r="N50" s="7">
+        <v>489.49</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B51" s="7">
+        <v>2226.21</v>
+      </c>
+      <c r="C51" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D51" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F31" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" s="10" t="b">
+      <c r="F51" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="H31" s="10" t="b">
+      <c r="H51" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="I31" s="10" t="b">
+      <c r="I51" s="8" t="b">
         <v>0</v>
       </c>
-      <c r="J31" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K31" s="8">
-        <v>2749.54</v>
-      </c>
-      <c r="L31" s="8">
-        <v>3674.5</v>
-      </c>
-      <c r="M31" s="8">
-        <v>3393.55</v>
-      </c>
-      <c r="N31" s="8">
-        <v>45.83</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B32" s="8">
-        <v>48139.58</v>
-      </c>
-      <c r="C32" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D32" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F32" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="G32" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I32" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J32" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K32" s="8">
-        <v>23903.61</v>
-      </c>
-      <c r="L32" s="8">
-        <v>11178.78</v>
-      </c>
-      <c r="M32" s="8">
-        <v>12264.43</v>
-      </c>
-      <c r="N32" s="8">
-        <v>792.76</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B33" s="8">
-        <v>8715.35</v>
-      </c>
-      <c r="C33" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D33" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="E33" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="F33" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="G33" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H33" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I33" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J33" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="K33" s="8">
-        <v>3834.88</v>
-      </c>
-      <c r="L33" s="8">
-        <v>2004.59</v>
-      </c>
-      <c r="M33" s="8">
-        <v>2789.0</v>
-      </c>
-      <c r="N33" s="8">
-        <v>86.88</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B34" s="8">
-        <v>3742.79</v>
-      </c>
-      <c r="C34" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D34" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F34" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G34" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H34" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I34" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J34" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K34" s="8">
-        <v>1646.83</v>
-      </c>
-      <c r="L34" s="8">
-        <v>860.84</v>
-      </c>
-      <c r="M34" s="8">
-        <v>1197.69</v>
-      </c>
-      <c r="N34" s="8">
-        <v>37.42</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B35" s="8">
-        <v>19801.0</v>
-      </c>
-      <c r="C35" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D35" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F35" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="G35" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I35" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J35" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K35" s="8">
-        <v>8712.44</v>
-      </c>
-      <c r="L35" s="8">
-        <v>4554.23</v>
-      </c>
-      <c r="M35" s="8">
-        <v>6336.32</v>
-      </c>
-      <c r="N35" s="8">
-        <v>198.01</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B36" s="8">
-        <v>4187.86</v>
-      </c>
-      <c r="C36" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D36" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F36" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G36" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H36" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I36" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J36" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K36" s="8">
-        <v>2443.24</v>
-      </c>
-      <c r="L36" s="8">
-        <v>496.53</v>
-      </c>
-      <c r="M36" s="8">
-        <v>1219.85</v>
-      </c>
-      <c r="N36" s="8">
-        <v>28.23</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B37" s="8">
-        <v>2524.91</v>
-      </c>
-      <c r="C37" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D37" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F37" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G37" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I37" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J37" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K37" s="8">
-        <v>1110.96</v>
-      </c>
-      <c r="L37" s="8">
-        <v>580.73</v>
-      </c>
-      <c r="M37" s="8">
-        <v>807.97</v>
-      </c>
-      <c r="N37" s="8">
-        <v>25.25</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B38" s="8">
-        <v>4696.11</v>
-      </c>
-      <c r="C38" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D38" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F38" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G38" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="H38" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I38" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J38" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K38" s="8">
-        <v>2194.53</v>
-      </c>
-      <c r="L38" s="8">
-        <v>1323.29</v>
-      </c>
-      <c r="M38" s="8">
-        <v>1167.8</v>
-      </c>
-      <c r="N38" s="8">
-        <v>10.49</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B39" s="8">
-        <v>21689.28</v>
-      </c>
-      <c r="C39" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D39" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F39" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G39" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I39" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J39" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K39" s="8">
-        <v>11277.07</v>
-      </c>
-      <c r="L39" s="8">
-        <v>3791.42</v>
-      </c>
-      <c r="M39" s="8">
-        <v>6427.99</v>
-      </c>
-      <c r="N39" s="8">
-        <v>192.79</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="B40" s="8">
-        <v>20527.38</v>
-      </c>
-      <c r="C40" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D40" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E40" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F40" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H40" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I40" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J40" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K40" s="8">
-        <v>3650.8</v>
-      </c>
-      <c r="L40" s="8">
-        <v>5707.92</v>
-      </c>
-      <c r="M40" s="8">
-        <v>10576.26</v>
-      </c>
-      <c r="N40" s="8">
-        <v>592.41</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B41" s="8">
-        <v>8307.15</v>
-      </c>
-      <c r="C41" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D41" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E41" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F41" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G41" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I41" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J41" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K41" s="8">
-        <v>5244.19</v>
-      </c>
-      <c r="L41" s="8">
-        <v>677.21</v>
-      </c>
-      <c r="M41" s="8">
-        <v>2277.39</v>
-      </c>
-      <c r="N41" s="8">
-        <v>108.36</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="B42" s="8">
-        <v>5793.88</v>
-      </c>
-      <c r="C42" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D42" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F42" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G42" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H42" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I42" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J42" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K42" s="8">
-        <v>2491.37</v>
-      </c>
-      <c r="L42" s="8">
-        <v>2665.18</v>
-      </c>
-      <c r="M42" s="8">
-        <v>579.39</v>
-      </c>
-      <c r="N42" s="8">
-        <v>57.94</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B43" s="8">
-        <v>5508.14</v>
-      </c>
-      <c r="C43" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D43" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="F43" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="G43" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I43" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J43" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="K43" s="8">
-        <v>2423.58</v>
-      </c>
-      <c r="L43" s="8">
-        <v>1266.87</v>
-      </c>
-      <c r="M43" s="8">
-        <v>1762.61</v>
-      </c>
-      <c r="N43" s="8">
-        <v>55.08</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B44" s="8">
-        <v>10208.23</v>
-      </c>
-      <c r="C44" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D44" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F44" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G44" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H44" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I44" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J44" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K44" s="8">
-        <v>4090.31</v>
-      </c>
-      <c r="L44" s="8">
-        <v>2064.78</v>
-      </c>
-      <c r="M44" s="8">
-        <v>3963.39</v>
-      </c>
-      <c r="N44" s="8">
-        <v>89.75</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B45" s="8">
-        <v>11181.33</v>
-      </c>
-      <c r="C45" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D45" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F45" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G45" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H45" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I45" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J45" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K45" s="8">
-        <v>7228.49</v>
-      </c>
-      <c r="L45" s="8">
-        <v>554.05</v>
-      </c>
-      <c r="M45" s="8">
-        <v>3322.33</v>
-      </c>
-      <c r="N45" s="8">
-        <v>76.46</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B46" s="8">
-        <v>15914.36</v>
-      </c>
-      <c r="C46" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D46" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F46" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="G46" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H46" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I46" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J46" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="K46" s="8">
-        <v>8727.37</v>
-      </c>
-      <c r="L46" s="8">
-        <v>355.16</v>
-      </c>
-      <c r="M46" s="8">
-        <v>6523.94</v>
-      </c>
-      <c r="N46" s="8">
-        <v>307.88</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B47" s="8">
-        <v>4044.86</v>
-      </c>
-      <c r="C47" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D47" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F47" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G47" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H47" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I47" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J47" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K47" s="8">
-        <v>3308.82</v>
-      </c>
-      <c r="L47" s="8">
-        <v>136.9</v>
-      </c>
-      <c r="M47" s="8">
-        <v>599.05</v>
-      </c>
-      <c r="N47" s="8">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B48" s="8">
-        <v>98897.61</v>
-      </c>
-      <c r="C48" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D48" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="F48" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="G48" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H48" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I48" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J48" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="K48" s="8">
-        <v>43514.95</v>
-      </c>
-      <c r="L48" s="8">
-        <v>22746.45</v>
-      </c>
-      <c r="M48" s="8">
-        <v>31647.23</v>
-      </c>
-      <c r="N48" s="8">
-        <v>988.98</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="B49" s="8">
-        <v>73107.65</v>
-      </c>
-      <c r="C49" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="D49" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="F49" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="G49" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H49" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I49" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J49" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="K49" s="8">
-        <v>32167.37</v>
-      </c>
-      <c r="L49" s="8">
-        <v>16814.76</v>
-      </c>
-      <c r="M49" s="8">
-        <v>23394.44</v>
-      </c>
-      <c r="N49" s="8">
-        <v>731.08</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B50" s="8">
-        <v>16316.21</v>
-      </c>
-      <c r="C50" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D50" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E50" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="F50" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="G50" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H50" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I50" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J50" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="K50" s="8">
-        <v>8158.11</v>
-      </c>
-      <c r="L50" s="8">
-        <v>5710.67</v>
-      </c>
-      <c r="M50" s="8">
-        <v>1957.95</v>
-      </c>
-      <c r="N50" s="8">
-        <v>489.49</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B51" s="8">
-        <v>2226.21</v>
-      </c>
-      <c r="C51" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="D51" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="E51" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F51" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="G51" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H51" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="I51" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J51" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K51" s="8">
+      <c r="J51" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K51" s="7">
         <v>1094.34</v>
       </c>
-      <c r="L51" s="8">
+      <c r="L51" s="7">
         <v>247.09</v>
       </c>
-      <c r="M51" s="8">
+      <c r="M51" s="7">
         <v>777.31</v>
       </c>
-      <c r="N51" s="8">
+      <c r="N51" s="7">
         <v>107.47</v>
       </c>
     </row>
@@ -12362,28 +12362,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>23</v>
@@ -12400,2257 +12400,2257 @@
       <c r="N1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="O1" s="5"/>
+      <c r="O1" s="6"/>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="10">
         <v>51.0</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="10">
         <v>9.0</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="10">
         <v>5.0</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="10">
         <v>1.0</v>
       </c>
-      <c r="F2" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G2" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H2" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I2" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J2" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K2" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L2" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M2" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N2" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O2" s="5"/>
+      <c r="F2" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G2" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H2" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I2" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J2" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K2" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L2" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M2" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N2" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O2" s="6"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="10">
         <v>66.0</v>
       </c>
-      <c r="C3" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="D3" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="E3" s="9">
+      <c r="C3" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="D3" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="E3" s="10">
         <v>17.0</v>
       </c>
-      <c r="F3" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G3" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H3" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I3" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J3" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K3" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L3" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M3" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N3" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O3" s="5"/>
+      <c r="F3" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G3" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H3" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I3" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J3" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K3" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L3" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M3" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N3" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O3" s="6"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="10">
         <v>37.0</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="10">
         <v>9.0</v>
       </c>
-      <c r="D4" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="F4" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G4" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H4" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I4" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J4" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K4" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L4" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M4" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N4" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O4" s="5"/>
+      <c r="D4" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="E4" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="F4" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G4" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H4" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I4" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J4" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K4" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L4" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M4" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N4" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O4" s="6"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="10">
         <v>68.0</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="10">
         <v>17.0</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="10">
         <v>2.0</v>
       </c>
-      <c r="E5" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="F5" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G5" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H5" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I5" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J5" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K5" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L5" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M5" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N5" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O5" s="5"/>
+      <c r="E5" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="F5" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G5" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H5" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I5" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J5" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K5" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L5" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M5" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N5" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O5" s="6"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="10">
         <v>242.0</v>
       </c>
-      <c r="C6" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="D6" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="F6" s="9">
+      <c r="C6" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="D6" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="E6" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="10">
         <v>1.0</v>
       </c>
-      <c r="G6" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H6" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I6" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J6" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K6" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L6" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M6" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N6" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O6" s="5"/>
+      <c r="G6" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H6" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I6" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J6" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K6" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L6" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M6" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N6" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O6" s="6"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="10">
         <v>41.0</v>
       </c>
-      <c r="C7" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="D7" s="9">
+      <c r="C7" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="D7" s="10">
         <v>1.0</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="10">
         <v>1.0</v>
       </c>
-      <c r="F7" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G7" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H7" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I7" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J7" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K7" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L7" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M7" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N7" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O7" s="5"/>
+      <c r="F7" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G7" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H7" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I7" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J7" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K7" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L7" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M7" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N7" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O7" s="6"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="10">
         <v>116.0</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="10">
         <v>80.0</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="10">
         <v>22.0</v>
       </c>
-      <c r="E8" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="F8" s="9">
+      <c r="E8" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="10">
         <v>9.0</v>
       </c>
-      <c r="G8" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H8" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I8" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J8" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K8" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L8" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M8" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N8" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O8" s="5"/>
+      <c r="G8" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H8" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I8" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J8" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K8" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L8" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M8" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N8" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O8" s="6"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="10">
         <v>158.0</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="10">
         <v>5.0</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="10">
         <v>6.0</v>
       </c>
-      <c r="E9" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="F9" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G9" s="9">
+      <c r="E9" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G9" s="10">
         <v>2.0</v>
       </c>
-      <c r="H9" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I9" s="9">
+      <c r="H9" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I9" s="10">
         <v>14.0</v>
       </c>
-      <c r="J9" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K9" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L9" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M9" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N9" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O9" s="5"/>
+      <c r="J9" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K9" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L9" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M9" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N9" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O9" s="6"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="10">
         <v>81.0</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="10">
         <v>30.0</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="10">
         <v>14.0</v>
       </c>
-      <c r="E10" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="F10" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G10" s="9">
+      <c r="E10" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G10" s="10">
         <v>1.0</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="10">
         <v>3.0</v>
       </c>
-      <c r="I10" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J10" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K10" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L10" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M10" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N10" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O10" s="5"/>
+      <c r="I10" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J10" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K10" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L10" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M10" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N10" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O10" s="6"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="10">
         <v>359.0</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="10">
         <v>8.0</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="10">
         <v>2.0</v>
       </c>
-      <c r="E11" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="F11" s="9">
+      <c r="E11" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="F11" s="10">
         <v>1.0</v>
       </c>
-      <c r="G11" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H11" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I11" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J11" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K11" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L11" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M11" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N11" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O11" s="5"/>
+      <c r="G11" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H11" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I11" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J11" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K11" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L11" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M11" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N11" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O11" s="6"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="10">
         <v>34.0</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="10">
         <v>20.0</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="10">
         <v>26.0</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="10">
         <v>76.0</v>
       </c>
-      <c r="F12" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G12" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H12" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I12" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J12" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K12" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L12" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M12" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N12" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O12" s="5"/>
+      <c r="F12" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G12" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H12" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I12" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J12" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K12" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L12" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M12" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N12" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O12" s="6"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="10">
         <v>15.0</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="10">
         <v>40.0</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="10">
         <v>2.0</v>
       </c>
-      <c r="E13" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="F13" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G13" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H13" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I13" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J13" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K13" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L13" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M13" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N13" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O13" s="5"/>
+      <c r="E13" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G13" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H13" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I13" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J13" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K13" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L13" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M13" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N13" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O13" s="6"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="10">
         <v>76.0</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="10">
         <v>14.0</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="10">
         <v>34.0</v>
       </c>
-      <c r="E14" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="F14" s="9">
+      <c r="E14" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="F14" s="10">
         <v>7.0</v>
       </c>
-      <c r="G14" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H14" s="9">
+      <c r="G14" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H14" s="10">
         <v>6.0</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="10">
         <v>1.0</v>
       </c>
-      <c r="J14" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K14" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L14" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M14" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N14" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O14" s="5"/>
+      <c r="J14" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K14" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L14" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M14" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N14" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O14" s="6"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="10">
         <v>263.0</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="10">
         <v>81.0</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="10">
         <v>10.0</v>
       </c>
-      <c r="E15" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="F15" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G15" s="9">
+      <c r="E15" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="F15" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G15" s="10">
         <v>1.0</v>
       </c>
-      <c r="H15" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I15" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J15" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K15" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L15" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M15" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N15" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O15" s="5"/>
+      <c r="H15" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I15" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J15" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K15" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L15" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M15" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N15" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O15" s="6"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16" s="9">
+      <c r="A16" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="10">
         <v>140.0</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="10">
         <v>4.0</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="10">
         <v>38.0</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="10">
         <v>34.0</v>
       </c>
-      <c r="F16" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G16" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H16" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I16" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J16" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K16" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L16" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M16" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N16" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O16" s="5"/>
+      <c r="F16" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G16" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H16" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I16" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J16" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K16" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L16" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M16" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N16" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="6"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="9">
+      <c r="A17" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="10">
         <v>48.0</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="10">
         <v>38.0</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="10">
         <v>15.0</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="10">
         <v>6.0</v>
       </c>
-      <c r="F17" s="9">
+      <c r="F17" s="10">
         <v>12.0</v>
       </c>
-      <c r="G17" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H17" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I17" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J17" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K17" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L17" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M17" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N17" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O17" s="5"/>
+      <c r="G17" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H17" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I17" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J17" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K17" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L17" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M17" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N17" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O17" s="6"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="10">
         <v>188.0</v>
       </c>
-      <c r="C18" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="D18" s="9">
+      <c r="C18" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="D18" s="10">
         <v>6.0</v>
       </c>
-      <c r="E18" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="F18" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G18" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H18" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I18" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J18" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K18" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L18" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M18" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N18" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O18" s="5"/>
+      <c r="E18" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="F18" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G18" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H18" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I18" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J18" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K18" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L18" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M18" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N18" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O18" s="6"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="10">
         <v>453.0</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="10">
         <v>22.0</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="10">
         <v>52.0</v>
       </c>
-      <c r="E19" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="F19" s="9">
+      <c r="E19" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="F19" s="10">
         <v>73.0</v>
       </c>
-      <c r="G19" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H19" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I19" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J19" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K19" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L19" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M19" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N19" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O19" s="5"/>
+      <c r="G19" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H19" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I19" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J19" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K19" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L19" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M19" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N19" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O19" s="6"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="9">
+      <c r="B20" s="10">
         <v>184.0</v>
       </c>
-      <c r="C20" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="D20" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="E20" s="9">
+      <c r="C20" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="D20" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="E20" s="10">
         <v>21.0</v>
       </c>
-      <c r="F20" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G20" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H20" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I20" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J20" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K20" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L20" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M20" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N20" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O20" s="5"/>
+      <c r="F20" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G20" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H20" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I20" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J20" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K20" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L20" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M20" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N20" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O20" s="6"/>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B21" s="10">
         <v>168.0</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="10">
         <v>1.0</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="10">
         <v>7.0</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="10">
         <v>125.0</v>
       </c>
-      <c r="F21" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G21" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H21" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I21" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J21" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K21" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L21" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M21" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N21" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O21" s="5"/>
+      <c r="F21" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G21" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H21" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I21" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J21" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K21" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L21" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M21" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N21" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O21" s="6"/>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B22" s="10">
         <v>206.0</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="10">
         <v>18.0</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="10">
         <v>12.0</v>
       </c>
-      <c r="E22" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="F22" s="9">
+      <c r="E22" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="F22" s="10">
         <v>8.0</v>
       </c>
-      <c r="G22" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H22" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I22" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J22" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K22" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L22" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M22" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N22" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O22" s="5"/>
+      <c r="G22" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H22" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I22" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J22" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K22" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L22" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M22" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N22" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O22" s="6"/>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="10">
         <v>682.0</v>
       </c>
-      <c r="C23" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="D23" s="9">
+      <c r="C23" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="D23" s="10">
         <v>33.0</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="10">
         <v>1.0</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="10">
         <v>1.0</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="10">
         <v>1.0</v>
       </c>
-      <c r="H23" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I23" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J23" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K23" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L23" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M23" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N23" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O23" s="5"/>
+      <c r="H23" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I23" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J23" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K23" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L23" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M23" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N23" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O23" s="6"/>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B24" s="10">
         <v>146.0</v>
       </c>
-      <c r="C24" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="D24" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="E24" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="F24" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G24" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H24" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I24" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J24" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K24" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L24" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M24" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N24" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O24" s="5"/>
+      <c r="C24" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="D24" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="E24" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="F24" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G24" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H24" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I24" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J24" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K24" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L24" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M24" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N24" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O24" s="6"/>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="9">
+      <c r="B25" s="10">
         <v>20.0</v>
       </c>
-      <c r="C25" s="9">
+      <c r="C25" s="10">
         <v>66.0</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="10">
         <v>14.0</v>
       </c>
-      <c r="E25" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="F25" s="9">
+      <c r="E25" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="F25" s="10">
         <v>1.0</v>
       </c>
-      <c r="G25" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H25" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I25" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J25" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K25" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L25" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M25" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N25" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O25" s="5"/>
+      <c r="G25" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H25" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I25" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J25" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K25" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L25" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M25" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N25" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O25" s="6"/>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B26" s="9">
+      <c r="B26" s="10">
         <v>454.0</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="10">
         <v>83.0</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="10">
         <v>33.0</v>
       </c>
-      <c r="E26" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="F26" s="9">
+      <c r="E26" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="F26" s="10">
         <v>2.0</v>
       </c>
-      <c r="G26" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H26" s="9">
+      <c r="G26" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H26" s="10">
         <v>1.0</v>
       </c>
-      <c r="I26" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J26" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K26" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L26" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M26" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N26" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O26" s="5"/>
+      <c r="I26" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J26" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K26" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L26" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M26" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N26" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O26" s="6"/>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B27" s="9">
+      <c r="B27" s="10">
         <v>67.0</v>
       </c>
-      <c r="C27" s="9">
+      <c r="C27" s="10">
         <v>26.0</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="10">
         <v>10.0</v>
       </c>
-      <c r="E27" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="F27" s="9">
+      <c r="E27" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="F27" s="10">
         <v>8.0</v>
       </c>
-      <c r="G27" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H27" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I27" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J27" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K27" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L27" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M27" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N27" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O27" s="5"/>
+      <c r="G27" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H27" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I27" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J27" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K27" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L27" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M27" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N27" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O27" s="6"/>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B28" s="9">
+      <c r="B28" s="10">
         <v>62.0</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28" s="10">
         <v>56.0</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="10">
         <v>65.0</v>
       </c>
-      <c r="E28" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="F28" s="9">
+      <c r="E28" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="F28" s="10">
         <v>3.0</v>
       </c>
-      <c r="G28" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H28" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I28" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J28" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K28" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L28" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M28" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N28" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O28" s="5"/>
+      <c r="G28" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H28" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I28" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J28" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K28" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L28" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M28" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N28" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O28" s="6"/>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="10">
         <v>35.0</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C29" s="10">
         <v>78.0</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="10">
         <v>40.0</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="10">
         <v>60.0</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="10">
         <v>18.0</v>
       </c>
-      <c r="G29" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H29" s="9">
+      <c r="G29" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H29" s="10">
         <v>2.0</v>
       </c>
-      <c r="I29" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J29" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K29" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L29" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M29" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N29" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O29" s="5"/>
+      <c r="I29" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J29" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K29" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L29" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M29" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N29" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O29" s="6"/>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B30" s="10">
         <v>423.0</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C30" s="10">
         <v>34.0</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="10">
         <v>179.0</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E30" s="10">
         <v>2.0</v>
       </c>
-      <c r="F30" s="9">
+      <c r="F30" s="10">
         <v>22.0</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="10">
         <v>2.0</v>
       </c>
-      <c r="H30" s="9">
+      <c r="H30" s="10">
         <v>2.0</v>
       </c>
-      <c r="I30" s="9">
+      <c r="I30" s="10">
         <v>1.0</v>
       </c>
-      <c r="J30" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K30" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L30" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M30" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N30" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O30" s="5"/>
+      <c r="J30" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K30" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L30" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M30" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N30" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O30" s="6"/>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B31" s="10">
         <v>94.0</v>
       </c>
-      <c r="C31" s="9">
+      <c r="C31" s="10">
         <v>8.0</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="10">
         <v>3.0</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="10">
         <v>13.0</v>
       </c>
-      <c r="F31" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G31" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H31" s="9">
+      <c r="F31" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G31" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H31" s="10">
         <v>2.0</v>
       </c>
-      <c r="I31" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J31" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K31" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L31" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M31" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N31" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O31" s="5"/>
+      <c r="I31" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J31" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K31" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L31" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M31" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N31" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O31" s="6"/>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32" s="10">
         <v>357.0</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="10">
         <v>68.0</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="10">
         <v>35.0</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="10">
         <v>32.0</v>
       </c>
-      <c r="F32" s="9">
+      <c r="F32" s="10">
         <v>2.0</v>
       </c>
-      <c r="G32" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H32" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I32" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J32" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K32" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L32" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M32" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N32" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O32" s="5"/>
+      <c r="G32" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H32" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I32" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J32" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K32" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L32" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M32" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N32" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O32" s="6"/>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="B33" s="9">
+      <c r="B33" s="10">
         <v>32.0</v>
       </c>
-      <c r="C33" s="9">
+      <c r="C33" s="10">
         <v>16.0</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D33" s="10">
         <v>7.0</v>
       </c>
-      <c r="E33" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="F33" s="9">
+      <c r="E33" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="F33" s="10">
         <v>2.0</v>
       </c>
-      <c r="G33" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H33" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I33" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J33" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K33" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L33" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M33" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N33" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O33" s="5"/>
+      <c r="G33" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H33" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I33" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J33" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K33" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L33" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M33" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N33" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O33" s="6"/>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B34" s="9">
+      <c r="B34" s="10">
         <v>91.0</v>
       </c>
-      <c r="C34" s="9">
+      <c r="C34" s="10">
         <v>11.0</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="10">
         <v>1.0</v>
       </c>
-      <c r="E34" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="F34" s="9">
+      <c r="E34" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="F34" s="10">
         <v>1.0</v>
       </c>
-      <c r="G34" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H34" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I34" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J34" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K34" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L34" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M34" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N34" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O34" s="5"/>
+      <c r="G34" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H34" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I34" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J34" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K34" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L34" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M34" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N34" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O34" s="6"/>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B35" s="9">
+      <c r="B35" s="10">
         <v>81.0</v>
       </c>
-      <c r="C35" s="9">
+      <c r="C35" s="10">
         <v>106.0</v>
       </c>
-      <c r="D35" s="9">
+      <c r="D35" s="10">
         <v>52.0</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E35" s="10">
         <v>29.0</v>
       </c>
-      <c r="F35" s="9">
+      <c r="F35" s="10">
         <v>6.0</v>
       </c>
-      <c r="G35" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H35" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I35" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J35" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K35" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L35" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M35" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N35" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O35" s="5"/>
+      <c r="G35" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H35" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I35" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J35" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K35" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L35" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M35" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N35" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O35" s="6"/>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B36" s="9">
+      <c r="B36" s="10">
         <v>17.0</v>
       </c>
-      <c r="C36" s="9">
+      <c r="C36" s="10">
         <v>5.0</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="10">
         <v>2.0</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E36" s="10">
         <v>121.0</v>
       </c>
-      <c r="F36" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G36" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H36" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I36" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J36" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K36" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L36" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M36" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N36" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O36" s="5"/>
+      <c r="F36" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G36" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H36" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I36" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J36" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K36" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L36" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M36" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N36" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O36" s="6"/>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B37" s="9">
+      <c r="B37" s="10">
         <v>105.0</v>
       </c>
-      <c r="C37" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="D37" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="E37" s="9">
+      <c r="C37" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="D37" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="E37" s="10">
         <v>2.0</v>
       </c>
-      <c r="F37" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G37" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H37" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I37" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J37" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K37" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L37" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M37" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N37" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O37" s="5"/>
+      <c r="F37" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G37" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H37" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I37" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J37" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K37" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L37" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M37" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N37" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O37" s="6"/>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B38" s="9">
+      <c r="B38" s="10">
         <v>7.0</v>
       </c>
-      <c r="C38" s="9">
+      <c r="C38" s="10">
         <v>4.0</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="10">
         <v>8.0</v>
       </c>
-      <c r="E38" s="9">
+      <c r="E38" s="10">
         <v>4.0</v>
       </c>
-      <c r="F38" s="9">
+      <c r="F38" s="10">
         <v>2.0</v>
       </c>
-      <c r="G38" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H38" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I38" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J38" s="9">
+      <c r="G38" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H38" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I38" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J38" s="10">
         <v>3.0</v>
       </c>
-      <c r="K38" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L38" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M38" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N38" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O38" s="5"/>
+      <c r="K38" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L38" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M38" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N38" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O38" s="6"/>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B39" s="9">
+      <c r="B39" s="10">
         <v>239.0</v>
       </c>
-      <c r="C39" s="9">
+      <c r="C39" s="10">
         <v>11.0</v>
       </c>
-      <c r="D39" s="9">
+      <c r="D39" s="10">
         <v>6.0</v>
       </c>
-      <c r="E39" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="F39" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G39" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H39" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I39" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J39" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K39" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L39" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M39" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N39" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O39" s="5"/>
+      <c r="E39" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="F39" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G39" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H39" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I39" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J39" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K39" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L39" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M39" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N39" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O39" s="6"/>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="B40" s="9">
+      <c r="B40" s="10">
         <v>42.0</v>
       </c>
-      <c r="C40" s="9">
+      <c r="C40" s="10">
         <v>7.0</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D40" s="10">
         <v>9.0</v>
       </c>
-      <c r="E40" s="9">
+      <c r="E40" s="10">
         <v>12.0</v>
       </c>
-      <c r="F40" s="9">
+      <c r="F40" s="10">
         <v>8.0</v>
       </c>
-      <c r="G40" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H40" s="9">
+      <c r="G40" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H40" s="10">
         <v>7.0</v>
       </c>
-      <c r="I40" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J40" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K40" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L40" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M40" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N40" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O40" s="5"/>
+      <c r="I40" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J40" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K40" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L40" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M40" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N40" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O40" s="6"/>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="s">
+      <c r="A41" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="B41" s="9">
+      <c r="B41" s="10">
         <v>28.0</v>
       </c>
-      <c r="C41" s="9">
+      <c r="C41" s="10">
         <v>40.0</v>
       </c>
-      <c r="D41" s="9">
+      <c r="D41" s="10">
         <v>87.0</v>
       </c>
-      <c r="E41" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="F41" s="9">
+      <c r="E41" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="F41" s="10">
         <v>7.0</v>
       </c>
-      <c r="G41" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H41" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I41" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J41" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K41" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L41" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M41" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N41" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O41" s="5"/>
+      <c r="G41" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H41" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I41" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J41" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K41" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L41" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M41" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N41" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O41" s="6"/>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="s">
+      <c r="A42" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B42" s="9">
+      <c r="B42" s="10">
         <v>45.0</v>
       </c>
-      <c r="C42" s="9">
+      <c r="C42" s="10">
         <v>5.0</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="10">
         <v>4.0</v>
       </c>
-      <c r="E42" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="F42" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G42" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H42" s="9">
+      <c r="E42" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="F42" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G42" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H42" s="10">
         <v>11.0</v>
       </c>
-      <c r="I42" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J42" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K42" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L42" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M42" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N42" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O42" s="5"/>
+      <c r="I42" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J42" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K42" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L42" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M42" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N42" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O42" s="6"/>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="s">
+      <c r="A43" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="B43" s="9">
+      <c r="B43" s="10">
         <v>8.0</v>
       </c>
-      <c r="C43" s="9">
+      <c r="C43" s="10">
         <v>10.0</v>
       </c>
-      <c r="D43" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="E43" s="9">
+      <c r="D43" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="E43" s="10">
         <v>34.0</v>
       </c>
-      <c r="F43" s="9">
+      <c r="F43" s="10">
         <v>2.0</v>
       </c>
-      <c r="G43" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H43" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I43" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J43" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K43" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L43" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M43" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N43" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O43" s="5"/>
+      <c r="G43" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H43" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I43" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J43" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K43" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L43" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M43" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N43" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O43" s="6"/>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="s">
+      <c r="A44" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B44" s="9">
+      <c r="B44" s="10">
         <v>82.0</v>
       </c>
-      <c r="C44" s="9">
+      <c r="C44" s="10">
         <v>1.0</v>
       </c>
-      <c r="D44" s="9">
+      <c r="D44" s="10">
         <v>20.0</v>
       </c>
-      <c r="E44" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="F44" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G44" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H44" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I44" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J44" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K44" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L44" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M44" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N44" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O44" s="5"/>
+      <c r="E44" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="F44" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G44" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H44" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I44" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J44" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K44" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L44" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M44" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N44" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O44" s="6"/>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="s">
+      <c r="A45" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="B45" s="9">
+      <c r="B45" s="10">
         <v>67.0</v>
       </c>
-      <c r="C45" s="9">
+      <c r="C45" s="10">
         <v>31.0</v>
       </c>
-      <c r="D45" s="9">
+      <c r="D45" s="10">
         <v>30.0</v>
       </c>
-      <c r="E45" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="F45" s="9">
+      <c r="E45" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="F45" s="10">
         <v>1.0</v>
       </c>
-      <c r="G45" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H45" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I45" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J45" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K45" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L45" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M45" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N45" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O45" s="5"/>
+      <c r="G45" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H45" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I45" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J45" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K45" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L45" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M45" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N45" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O45" s="6"/>
     </row>
     <row r="46">
-      <c r="A46" s="7" t="s">
+      <c r="A46" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="B46" s="9">
+      <c r="B46" s="10">
         <v>10.0</v>
       </c>
-      <c r="C46" s="9">
+      <c r="C46" s="10">
         <v>16.0</v>
       </c>
-      <c r="D46" s="9">
+      <c r="D46" s="10">
         <v>3.0</v>
       </c>
-      <c r="E46" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="F46" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G46" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H46" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I46" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J46" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K46" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L46" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M46" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N46" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O46" s="5"/>
+      <c r="E46" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="F46" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G46" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H46" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I46" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J46" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K46" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L46" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M46" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N46" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O46" s="6"/>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="s">
+      <c r="A47" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B47" s="9">
+      <c r="B47" s="10">
         <v>8.0</v>
       </c>
-      <c r="C47" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="D47" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="E47" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="F47" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G47" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H47" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I47" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J47" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K47" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L47" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M47" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N47" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O47" s="5"/>
+      <c r="C47" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="D47" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="E47" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="F47" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G47" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H47" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I47" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J47" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K47" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L47" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M47" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N47" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O47" s="6"/>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="s">
+      <c r="A48" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="B48" s="9">
+      <c r="B48" s="10">
         <v>943.0</v>
       </c>
-      <c r="C48" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="D48" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="E48" s="9">
+      <c r="C48" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="D48" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="E48" s="10">
         <v>2.0</v>
       </c>
-      <c r="F48" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G48" s="9">
+      <c r="F48" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G48" s="10">
         <v>27.0</v>
       </c>
-      <c r="H48" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I48" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J48" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K48" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L48" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M48" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N48" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O48" s="5"/>
+      <c r="H48" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I48" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J48" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K48" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L48" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M48" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N48" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O48" s="6"/>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="s">
+      <c r="A49" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B49" s="9">
+      <c r="B49" s="10">
         <v>256.0</v>
       </c>
-      <c r="C49" s="9">
+      <c r="C49" s="10">
         <v>17.0</v>
       </c>
-      <c r="D49" s="9">
+      <c r="D49" s="10">
         <v>70.0</v>
       </c>
-      <c r="E49" s="9">
+      <c r="E49" s="10">
         <v>73.0</v>
       </c>
-      <c r="F49" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G49" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H49" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I49" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J49" s="9">
+      <c r="F49" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G49" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H49" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I49" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J49" s="10">
         <v>6.0</v>
       </c>
-      <c r="K49" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L49" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M49" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N49" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O49" s="5"/>
+      <c r="K49" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L49" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M49" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N49" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O49" s="6"/>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="s">
+      <c r="A50" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B50" s="9">
+      <c r="B50" s="10">
         <v>38.0</v>
       </c>
-      <c r="C50" s="9">
+      <c r="C50" s="10">
         <v>32.0</v>
       </c>
-      <c r="D50" s="9">
+      <c r="D50" s="10">
         <v>40.0</v>
       </c>
-      <c r="E50" s="9">
+      <c r="E50" s="10">
         <v>10.0</v>
       </c>
-      <c r="F50" s="9">
+      <c r="F50" s="10">
         <v>10.0</v>
       </c>
-      <c r="G50" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H50" s="9">
+      <c r="G50" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H50" s="10">
         <v>7.0</v>
       </c>
-      <c r="I50" s="9">
+      <c r="I50" s="10">
         <v>5.0</v>
       </c>
-      <c r="J50" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K50" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L50" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M50" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N50" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O50" s="5"/>
+      <c r="J50" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K50" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L50" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M50" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N50" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O50" s="6"/>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="s">
+      <c r="A51" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="B51" s="9">
+      <c r="B51" s="10">
         <v>7.0</v>
       </c>
-      <c r="C51" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="D51" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="E51" s="9">
+      <c r="C51" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="D51" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="E51" s="10">
         <v>57.0</v>
       </c>
-      <c r="F51" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="G51" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="H51" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="I51" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="J51" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="K51" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="L51" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="M51" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="N51" s="9">
-        <v>0.0</v>
-      </c>
-      <c r="O51" s="5"/>
+      <c r="F51" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="G51" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="H51" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="I51" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="J51" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="K51" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="L51" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="M51" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="N51" s="10">
+        <v>0.0</v>
+      </c>
+      <c r="O51" s="6"/>
     </row>
     <row r="52">
       <c r="A52" s="12"/>
@@ -14667,41 +14667,41 @@
       <c r="L52" s="13"/>
       <c r="M52" s="13"/>
       <c r="N52" s="13"/>
-      <c r="O52" s="5"/>
+      <c r="O52" s="6"/>
     </row>
     <row r="53">
       <c r="A53" s="12"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="5"/>
-      <c r="H53" s="5"/>
-      <c r="I53" s="5"/>
-      <c r="J53" s="5"/>
-      <c r="K53" s="5"/>
-      <c r="L53" s="5"/>
-      <c r="M53" s="5"/>
-      <c r="N53" s="5"/>
-      <c r="O53" s="5"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="10"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="6"/>
+      <c r="K53" s="6"/>
+      <c r="L53" s="6"/>
+      <c r="M53" s="6"/>
+      <c r="N53" s="6"/>
+      <c r="O53" s="6"/>
     </row>
     <row r="54">
       <c r="A54" s="12"/>
-      <c r="B54" s="5"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-      <c r="H54" s="5"/>
-      <c r="I54" s="5"/>
-      <c r="J54" s="5"/>
-      <c r="K54" s="5"/>
-      <c r="L54" s="5"/>
-      <c r="M54" s="5"/>
-      <c r="N54" s="5"/>
-      <c r="O54" s="5"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="6"/>
+      <c r="M54" s="6"/>
+      <c r="N54" s="6"/>
+      <c r="O54" s="6"/>
     </row>
     <row r="55">
       <c r="A55" s="14"/>
